--- a/01-Customer Profile/customer-profile-testcases.xlsx
+++ b/01-Customer Profile/customer-profile-testcases.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="502">
   <si>
     <t>SN</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>UI Design</t>
-  </si>
-  <si>
-    <t>Data Test</t>
   </si>
   <si>
     <t>Test Result</t>
@@ -189,6 +186,9 @@
 - Delete button</t>
   </si>
   <si>
+    <t>Ketwadee Kaewmanee</t>
+  </si>
+  <si>
     <t>TS-01_TS-01_TC-02-CC Super App-Customer Profile</t>
   </si>
   <si>
@@ -502,7 +502,7 @@
     <t>Click on "Save"</t>
   </si>
   <si>
-    <t>Redirect to Customer List Page and Display Toast "Success"</t>
+    <t>Redirect to Customer List Page and Display Toast “Success”</t>
   </si>
   <si>
     <t>TS-02_TS-02_TC-09-CC Super App-Customer Profile</t>
@@ -682,7 +682,8 @@
   <si>
     <t xml:space="preserve">Login User: ketwadee 
 and Navigate to "Customer List Page"
-and Click on "Edit Customer" of "Wannapa Suksai"</t>
+and Search keyword "Wannapa Suksai"
+and Click on "Edit" of "Wannapa Suksai"</t>
   </si>
   <si>
     <t xml:space="preserve">The Edit form displays the values that were added
@@ -1131,7 +1132,7 @@
     <t>Click on "Confirm"</t>
   </si>
   <si>
-    <t>Display Toast "Success"</t>
+    <t>Display Toast “Success”</t>
   </si>
   <si>
     <t>TS-04_TS-04_TC-06-CC Super App-Customer Profile</t>
@@ -1409,6 +1410,12 @@
 and Click on Save</t>
   </si>
   <si>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>Screen Recording 2569-06-23 at 15.16.36.mov</t>
+  </si>
+  <si>
     <t>TA-01_TA-02_TC-01-CC Super App-Customer Profile</t>
   </si>
   <si>
@@ -1442,6 +1449,9 @@
     <t>Display message "No results found."</t>
   </si>
   <si>
+    <t>image.png</t>
+  </si>
+  <si>
     <t>TA-02_TA-03_TC-01-CC Super App-Customer Profile</t>
   </si>
   <si>
@@ -1466,7 +1476,7 @@
 and Click on Save</t>
   </si>
   <si>
-    <t>Display error toast "Please enter an email address"</t>
+    <t>Display error toast “Please enter an email address”</t>
   </si>
   <si>
     <t>TA-03_TA-04_TC-01-CC Super App-Customer Profile</t>
@@ -1496,7 +1506,7 @@
 and Click on Save</t>
   </si>
   <si>
-    <t>Display error toast "Please enter a mobile number"</t>
+    <t>Display error toast “Please enter a mobile number”</t>
   </si>
   <si>
     <t>TA-04_TA-05_TC-01-CC Super App-Customer Profile</t>
@@ -1532,8 +1542,7 @@
 and Click on Save</t>
   </si>
   <si>
-    <t xml:space="preserve">TBC
-Display error toast "Duplicate email address"</t>
+    <t>Display error toast "Email already exists"</t>
   </si>
   <si>
     <t>TA-05_TA-06_TC-01-CC Super App-Customer Profile</t>
@@ -1563,8 +1572,7 @@
 and Click on Save</t>
   </si>
   <si>
-    <t xml:space="preserve">TBC
-Display error toast "Invalid email address format"</t>
+    <t>Display error toast “Invalid email format”</t>
   </si>
   <si>
     <t>TA-06_TA-07_TC-01-CC Super App-Customer Profile</t>
@@ -1595,8 +1603,7 @@
 and Click on Save</t>
   </si>
   <si>
-    <t xml:space="preserve">TBC
-Display error toast "Invalid citizen id format"</t>
+    <t>Display error toast “Invalid CitizenID format”</t>
   </si>
   <si>
     <t>TA-07_TA-08_TC-01-CC Super App-Customer Profile</t>
@@ -1655,8 +1662,7 @@
 and Click on Save</t>
   </si>
   <si>
-    <t xml:space="preserve">TBC
-Display error toast "Invalid date of birth format"</t>
+    <t>Future date is not selectable (calendar disables dates after today)</t>
   </si>
   <si>
     <t>TA-09_TA-11_TC-01-CC Super App-Customer Profile</t>
@@ -1668,7 +1674,7 @@
     <t>Verify error toast when adding a customer with a wrong photo format (PDF)</t>
   </si>
   <si>
-    <t>1. The format is not supported.</t>
+    <t>1. The photo file format is not supported.</t>
   </si>
   <si>
     <t>TA-11_TC-01</t>
@@ -1680,8 +1686,7 @@
     <t>Upload file contract.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">TBC
-Display error toast "Invalid upload photo file" and The file was not uploaded.</t>
+    <t>Display error toast “Invalid upload photo file”</t>
   </si>
   <si>
     <t>TA-10_TA-12_TC-01-CC Super App-Customer Profile</t>
@@ -1705,8 +1710,7 @@
     <t>Upload file photo_hd.jpg (4MB)</t>
   </si>
   <si>
-    <t xml:space="preserve">TBC
-Display error toast "The file size must not exceed 3MB." and The file was not uploaded.</t>
+    <t>Display error toast “Error” (UI generic) | API: File too large (&gt;3MB)</t>
   </si>
   <si>
     <t>TA-11_TA-13_TC-01-CC Super App-Customer Profile</t>
@@ -1775,6 +1779,9 @@
 and Click on Save</t>
   </si>
   <si>
+    <t>Display error toast “Email already exists”</t>
+  </si>
+  <si>
     <t>TA-12_TA-14_TC-01-CC Super App-Customer Profile</t>
   </si>
   <si>
@@ -1831,8 +1838,7 @@
     <t>Click on "Delete" of "Somchai Jaidee"</t>
   </si>
   <si>
-    <t xml:space="preserve">TBC
-Display error toast "The customer cannot be deleted."</t>
+    <t>Display error toast “Customer has active warranty products”</t>
   </si>
   <si>
     <t>TA-14_TA-17_TC-01-CC Super App-Customer Profile</t>
@@ -2017,13 +2023,380 @@
   <si>
     <t>Display message "No results found." in Cases Section</t>
   </si>
+  <si>
+    <t>TA-17_TA-06_TC-01--Customer Profile</t>
+  </si>
+  <si>
+    <t>TA-17</t>
+  </si>
+  <si>
+    <t>Verify error toast when adding a customer with a Invalid phone number format</t>
+  </si>
+  <si>
+    <t>1. Invalid phone number format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login User: ketwadee 
+and Navigate to "Customer List Page"
+and Click on "Add Customer"
+Fill in data
+- Email: darinee@gmail.co.th
+- Phone: darinee
+and Click on Save</t>
+  </si>
+  <si>
+    <t>Display error toast “Invalid mobile number format”</t>
+  </si>
+  <si>
+    <t>TS-09_TS-09_TC-01-CC Super App-Customer Profile</t>
+  </si>
+  <si>
+    <t>TS-09</t>
+  </si>
+  <si>
+    <t>User can navigate between pages and change the number of rows displayed per page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Pagination controls (Next/Previous/Rows per page)
+2. Next page navigation
+3. Previous page navigation
+4. Rows per page selector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login User: ketwadee
+Role &amp; Permission: All Permission - Contact Management
+----------------------------
+≥ 11 Customer records in system (to trigger multi-page pagination)
+Default rows per page: 10</t>
+  </si>
+  <si>
+    <t>Navigate to "Customer List Page" and verify pagination controls appear</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login User: ketwadee
+and Navigate to "Customer List Page"</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>TS-09_TS-09_TC-02-CC Super App-Customer Profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login User: ketwadee
+Role &amp; Permission: All Permission - Contact Management
+----------------------------
+≥ 11 Customer records in system
+Currently on Page 1 (rows per page = 10)</t>
+  </si>
+  <si>
+    <t>TS-09_TC-02</t>
+  </si>
+  <si>
+    <t>Click "Next Page" button — navigate to page 2</t>
+  </si>
+  <si>
+    <t>Click "Next" (&gt;) button on pagination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Display page 2 records (different from page 1)
+Page indicator updates (e.g., "11-20 of N" or "Page 2 of M")</t>
+  </si>
+  <si>
+    <t>TS-09_TS-09_TC-03-CC Super App-Customer Profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login User: ketwadee
+Role &amp; Permission: All Permission - Contact Management
+----------------------------
+≥ 11 Customer records in system
+Currently on Page 2 (clicked Next from Page 1)</t>
+  </si>
+  <si>
+    <t>Click "Previous Page" button — return to page 1</t>
+  </si>
+  <si>
+    <t>Click "Previous" (&lt;) button on pagination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Display page 1 records (same as original)
+Page indicator returns to page 1 (e.g., "1-10 of N" or "Page 1 of M")</t>
+  </si>
+  <si>
+    <t>TS-09_TS-09_TC-04-CC Super App-Customer Profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login User: ketwadee
+Role &amp; Permission: All Permission - Contact Management
+----------------------------
+≥ 26 Customer records in system
+Currently showing rows per page = 10 (default)</t>
+  </si>
+  <si>
+    <t>TS-09_TC-04</t>
+  </si>
+  <si>
+    <t>Select rows per page = 25 — table shows up to 25 rows</t>
+  </si>
+  <si>
+    <t>Select "25" from rows-per-page dropdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table displays ≤ 25 rows per page
+Page indicator updates (e.g., "1-25 of N")</t>
+  </si>
+  <si>
+    <t>TS-09_TS-09_TC-05-CC Super App-Customer Profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login User: ketwadee
+Role &amp; Permission: All Permission - Contact Management
+----------------------------
+≥ 26 Customer records in system
+Currently showing rows per page = 25</t>
+  </si>
+  <si>
+    <t>TS-09_TC-05</t>
+  </si>
+  <si>
+    <t>Select rows per page = 10 — table shows up to 10 rows</t>
+  </si>
+  <si>
+    <t>Select "10" from rows-per-page dropdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table displays ≤ 10 rows per page
+Page indicator updates (e.g., "1-10 of N")</t>
+  </si>
+  <si>
+    <t>TA-18_TA-20_TC-01-CC Super App-Customer Profile</t>
+  </si>
+  <si>
+    <t>TA-18</t>
+  </si>
+  <si>
+    <t>Verify Previous Page button is disabled when on the first page</t>
+  </si>
+  <si>
+    <t>1. Previous page button disabled on first page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login User: ketwadee
+Role &amp; Permission: All Permission - Contact Management
+----------------------------
+≥ 11 Customer records in system
+Currently on Page 1 (first page)</t>
+  </si>
+  <si>
+    <t>TA-20_TC-01</t>
+  </si>
+  <si>
+    <t>Previous button is disabled on page 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login User: ketwadee
+and Navigate to "Customer List Page"
+and Verify state of "Previous" (&lt;) button on page 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previous button is disabled (not clickable)
+Clicking Previous does not change the page
+Page indicator remains on page 1</t>
+  </si>
+  <si>
+    <t>TA-19_TA-21_TC-01-CC Super App-Customer Profile</t>
+  </si>
+  <si>
+    <t>TA-19</t>
+  </si>
+  <si>
+    <t>Verify Next Page button is disabled when on the last page</t>
+  </si>
+  <si>
+    <t>1. Next page button disabled on last page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login User: ketwadee
+Role &amp; Permission: All Permission - Contact Management
+----------------------------
+≥ 11 Customer records in system
+Navigated to last page</t>
+  </si>
+  <si>
+    <t>TA-21_TC-01</t>
+  </si>
+  <si>
+    <t>Next button is disabled on the last page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login User: ketwadee
+and Navigate to "Customer List Page"
+and Click "Next" repeatedly until reaching the last page
+and Verify state of "Next" (&gt;) button on last page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next button is disabled (not clickable)
+Clicking Next does not change the page
+Page indicator shows last page (e.g., "N-N of N")</t>
+  </si>
+  <si>
+    <t>TS-10_TS-10_TC-01-CC Super App-Customer Profile</t>
+  </si>
+  <si>
+    <t>TS-10</t>
+  </si>
+  <si>
+    <t>User can view Customer List in Table View (default) and switch to Grid View and back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Customer List Toggle View (Table / Grid)
+2. Default view = Table View (☰ icon active)
+3. Grid View icon (⊞) switches to Card layout
+4. Table View icon (☰) switches back to Table layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login User: ketwadee
+Role &amp; Permission: All Permission - Contact Management
+---------------------------------------------------
+Customer Data in System:
+≥1 Customer record exists (e.g. ana Yukinae / any seeded customer)</t>
+  </si>
+  <si>
+    <t>TS-10_TC-01</t>
+  </si>
+  <si>
+    <t>Navigate to Customer List — Table View is displayed by default</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table View is active by default:
+- Icon ☰ (Table View) is highlighted blue
+- Icon ⊞ (Grid View) is NOT highlighted
+- Table is displayed with columns: ลูกค้า / ติดต่อ / ผลิตภัณฑ์ / บริการ / ประเภท / เปิดใช้งาน
+- Action buttons per row: โทร / อีเมล / แชท / ดู / แก้ไข / ลบ</t>
+  </si>
+  <si>
+    <t>TS-10_TS-10_TC-02-CC Super App-Customer Profile</t>
+  </si>
+  <si>
+    <t>TS-10_TC-02</t>
+  </si>
+  <si>
+    <t>Click Grid View icon (⊞) — list switches to Grid/Card layout</t>
+  </si>
+  <si>
+    <t>Click the Grid View icon (⊞) at the top-left toggle area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grid View is active:
+- Icon ⊞ (Grid View) is highlighted blue
+- Icon ☰ (Table View) is NOT highlighted
+- Page displays Card layout (no table rows)
+- Each card shows: Profile photo · Customer name · Type badge (โกลด์/แพลทินัม/บรอนซ์/ซิลเวอร์) · Active status dot · Email · Phone · จำนวน ผลิตภัณฑ์ · จำนวน บริการ · Action buttons (โทร/อีเมล/แชท/ดู/แก้ไข/ลบ)</t>
+  </si>
+  <si>
+    <t>TS-10_TS-10_TC-03-CC Super App-Customer Profile</t>
+  </si>
+  <si>
+    <t>TS-10_TC-03</t>
+  </si>
+  <si>
+    <t>Click Table View icon (☰) — list switches back to Table layout</t>
+  </si>
+  <si>
+    <t>Click the Table View icon (☰) at the top-left toggle area</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table View is restored:
+- Icon ☰ (Table View) is highlighted blue
+- Icon ⊞ (Grid View) is NOT highlighted
+- Table is displayed with columns: ลูกค้า / ติดต่อ / ผลิตภัณฑ์ / บริการ / ประเภท / เปิดใช้งาน
+- Card layout is no longer visible</t>
+  </si>
+  <si>
+    <t>TS-08</t>
+  </si>
+  <si>
+    <t>Display fallback: no name → email, no type → N/A</t>
+  </si>
+  <si>
+    <t>ลูกค้าที่ไม่มี Type ต้องแสดง "N/A" ในช่อง Type</t>
+  </si>
+  <si>
+    <t>Login as Agent · seed customer NONAME (firstName/lastName/type ว่าง)</t>
+  </si>
+  <si>
+    <t>TS-08_TC-02</t>
+  </si>
+  <si>
+    <t>Customer ไม่มี Type → ช่อง Type แสดง "N/A"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. เปิด Customer Detail ของ customer ที่ไม่มี Type
+2. สังเกตช่อง Type</t>
+  </si>
+  <si>
+    <t>ช่อง Type แสดงข้อความ "N/A" (exact match)</t>
+  </si>
+  <si>
+    <t>Error toast "Invalid email format" (invalid email formats)</t>
+  </si>
+  <si>
+    <t>Email ที่ format ผิดต้องแสดง toast "Invalid email format"</t>
+  </si>
+  <si>
+    <t>Login as Agent · เปิดหน้า Add Customer · กรอก field อื่นครบ ยกเว้น email</t>
+  </si>
+  <si>
+    <t>TA-06_TC-02</t>
+  </si>
+  <si>
+    <t>Email "test@gmail" (no TLD) → "Invalid email format"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. กรอก Email = "test@gmail"
+2. กด Save</t>
+  </si>
+  <si>
+    <t>Toast แสดง "Invalid email format"</t>
+  </si>
+  <si>
+    <t>TA-06_TC-03</t>
+  </si>
+  <si>
+    <t>Email "test@@gmail.com" (double @) → "Invalid email format"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. กรอก Email = "test@@gmail.com"
+2. กด Save</t>
+  </si>
+  <si>
+    <t>TA-06_TC-04</t>
+  </si>
+  <si>
+    <t>Email "test@gmail.c" (TLD 1 char only) → "Invalid email format"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. กรอก Email = "test@gmail.c"
+2. กด Save</t>
+  </si>
+  <si>
+    <t>TA-06_TC-05</t>
+  </si>
+  <si>
+    <t>Email "test@.com" (domain starts with dot) → "Invalid email format"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. กรอก Email = "test@.com"
+2. กด Save</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/MM/yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -2065,12 +2438,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2079,7 +2453,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFEE3E2"/>
+          <bgColor rgb="FFFEF0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2354,13 +2728,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:X65"/>
-  <sheetFormatPr customHeight="1"/>
+  <dimension ref="A1:W81"/>
+  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
-    <col min="1" max="24" width="19" customWidth="1"/>
+    <col min="1" max="23" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" ht="13" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2430,79 +2804,79 @@
       <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="2" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
         <v>27</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>28</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>29</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>30</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>31</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>32</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>33</v>
       </c>
-      <c r="K2" t="s">
-        <v>34</v>
-      </c>
       <c r="L2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" t="s">
         <v>35</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>36</v>
       </c>
-      <c r="N2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="3" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>38</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>28</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>30</v>
-      </c>
-      <c r="H3" t="s">
-        <v>31</v>
       </c>
       <c r="I3" t="s">
         <v>39</v>
@@ -2511,10 +2885,10 @@
         <v>40</v>
       </c>
       <c r="K3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M3" t="s">
         <v>41</v>
@@ -2522,32 +2896,35 @@
       <c r="N3" t="s">
         <v>42</v>
       </c>
-      <c r="S3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="4" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" t="s">
         <v>27</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>28</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>30</v>
-      </c>
-      <c r="H4" t="s">
-        <v>31</v>
       </c>
       <c r="I4" t="s">
         <v>44</v>
@@ -2556,10 +2933,10 @@
         <v>45</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M4" t="s">
         <v>46</v>
@@ -2567,32 +2944,35 @@
       <c r="N4" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="5" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>47</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" t="s">
         <v>27</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>28</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>29</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>30</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
       </c>
       <c r="I5" t="s">
         <v>48</v>
@@ -2601,10 +2981,10 @@
         <v>49</v>
       </c>
       <c r="K5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M5" t="s">
         <v>50</v>
@@ -2612,32 +2992,35 @@
       <c r="N5" t="s">
         <v>42</v>
       </c>
-      <c r="S5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="6" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
         <v>27</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>28</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>29</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>30</v>
-      </c>
-      <c r="H6" t="s">
-        <v>31</v>
       </c>
       <c r="I6" t="s">
         <v>52</v>
@@ -2646,10 +3029,10 @@
         <v>53</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M6" t="s">
         <v>54</v>
@@ -2657,32 +3040,35 @@
       <c r="N6" t="s">
         <v>55</v>
       </c>
-      <c r="S6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="7" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>56</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
         <v>27</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>28</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>29</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>30</v>
-      </c>
-      <c r="H7" t="s">
-        <v>31</v>
       </c>
       <c r="I7" t="s">
         <v>57</v>
@@ -2691,10 +3077,10 @@
         <v>58</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M7" t="s">
         <v>59</v>
@@ -2702,32 +3088,35 @@
       <c r="N7" t="s">
         <v>42</v>
       </c>
-      <c r="S7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="8" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
         <v>27</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>28</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>29</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>30</v>
-      </c>
-      <c r="H8" t="s">
-        <v>31</v>
       </c>
       <c r="I8" t="s">
         <v>61</v>
@@ -2736,10 +3125,10 @@
         <v>62</v>
       </c>
       <c r="K8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M8" t="s">
         <v>63</v>
@@ -2747,32 +3136,35 @@
       <c r="N8" t="s">
         <v>64</v>
       </c>
-      <c r="S8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="9" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
         <v>27</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>28</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>29</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>30</v>
-      </c>
-      <c r="H9" t="s">
-        <v>31</v>
       </c>
       <c r="I9" t="s">
         <v>66</v>
@@ -2781,10 +3173,10 @@
         <v>67</v>
       </c>
       <c r="K9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M9" t="s">
         <v>68</v>
@@ -2792,32 +3184,35 @@
       <c r="N9" t="s">
         <v>69</v>
       </c>
-      <c r="S9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="10" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
         <v>27</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>28</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>29</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>30</v>
-      </c>
-      <c r="H10" t="s">
-        <v>31</v>
       </c>
       <c r="I10" t="s">
         <v>71</v>
@@ -2826,10 +3221,10 @@
         <v>72</v>
       </c>
       <c r="K10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M10" t="s">
         <v>73</v>
@@ -2837,32 +3232,35 @@
       <c r="N10" t="s">
         <v>74</v>
       </c>
-      <c r="S10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="11" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
         <v>27</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>28</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>29</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>30</v>
-      </c>
-      <c r="H11" t="s">
-        <v>31</v>
       </c>
       <c r="I11" t="s">
         <v>76</v>
@@ -2871,10 +3269,10 @@
         <v>77</v>
       </c>
       <c r="K11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M11" t="s">
         <v>78</v>
@@ -2882,20 +3280,23 @@
       <c r="N11" t="s">
         <v>79</v>
       </c>
-      <c r="S11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="12" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
         <v>81</v>
@@ -2916,10 +3317,10 @@
         <v>86</v>
       </c>
       <c r="K12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M12" t="s">
         <v>87</v>
@@ -2927,20 +3328,23 @@
       <c r="N12" t="s">
         <v>88</v>
       </c>
-      <c r="S12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="13" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
         <v>81</v>
@@ -2961,10 +3365,10 @@
         <v>91</v>
       </c>
       <c r="K13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M13" t="s">
         <v>92</v>
@@ -2972,20 +3376,23 @@
       <c r="N13" t="s">
         <v>93</v>
       </c>
-      <c r="S13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="14" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>94</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
         <v>81</v>
@@ -3006,10 +3413,10 @@
         <v>96</v>
       </c>
       <c r="K14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M14" t="s">
         <v>97</v>
@@ -3017,20 +3424,23 @@
       <c r="N14" t="s">
         <v>98</v>
       </c>
-      <c r="S14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="15" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>99</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" t="s">
         <v>81</v>
@@ -3051,10 +3461,10 @@
         <v>101</v>
       </c>
       <c r="K15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M15" t="s">
         <v>102</v>
@@ -3062,20 +3472,23 @@
       <c r="N15" t="s">
         <v>98</v>
       </c>
-      <c r="S15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="16" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>103</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" t="s">
         <v>81</v>
@@ -3096,10 +3509,10 @@
         <v>105</v>
       </c>
       <c r="K16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M16" t="s">
         <v>106</v>
@@ -3107,20 +3520,23 @@
       <c r="N16" t="s">
         <v>107</v>
       </c>
-      <c r="S16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="17" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>108</v>
       </c>
       <c r="B17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E17" t="s">
         <v>81</v>
@@ -3141,10 +3557,10 @@
         <v>110</v>
       </c>
       <c r="K17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M17" t="s">
         <v>111</v>
@@ -3152,20 +3568,23 @@
       <c r="N17" t="s">
         <v>98</v>
       </c>
-      <c r="S17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="18" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>112</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E18" t="s">
         <v>81</v>
@@ -3186,10 +3605,10 @@
         <v>114</v>
       </c>
       <c r="K18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M18" t="s">
         <v>115</v>
@@ -3197,20 +3616,23 @@
       <c r="N18" t="s">
         <v>98</v>
       </c>
-      <c r="S18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="19" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>116</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" t="s">
         <v>81</v>
@@ -3231,10 +3653,10 @@
         <v>118</v>
       </c>
       <c r="K19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M19" t="s">
         <v>119</v>
@@ -3242,20 +3664,23 @@
       <c r="N19" t="s">
         <v>120</v>
       </c>
-      <c r="S19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="20" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>121</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20" t="s">
         <v>81</v>
@@ -3276,10 +3701,10 @@
         <v>53</v>
       </c>
       <c r="K20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M20" t="s">
         <v>123</v>
@@ -3287,20 +3712,23 @@
       <c r="N20" t="s">
         <v>124</v>
       </c>
-      <c r="S20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="21" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>125</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" t="s">
         <v>81</v>
@@ -3321,10 +3749,10 @@
         <v>127</v>
       </c>
       <c r="K21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M21" t="s">
         <v>128</v>
@@ -3332,20 +3760,23 @@
       <c r="N21" t="s">
         <v>129</v>
       </c>
-      <c r="S21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="22" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>130</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E22" t="s">
         <v>81</v>
@@ -3366,10 +3797,10 @@
         <v>132</v>
       </c>
       <c r="K22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M22" t="s">
         <v>133</v>
@@ -3377,20 +3808,23 @@
       <c r="N22" t="s">
         <v>134</v>
       </c>
-      <c r="S22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="23" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>135</v>
       </c>
       <c r="B23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" t="s">
         <v>81</v>
@@ -3411,10 +3845,10 @@
         <v>137</v>
       </c>
       <c r="K23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M23" t="s">
         <v>138</v>
@@ -3422,20 +3856,23 @@
       <c r="N23" t="s">
         <v>139</v>
       </c>
-      <c r="S23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="24" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>140</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E24" t="s">
         <v>81</v>
@@ -3456,10 +3893,10 @@
         <v>142</v>
       </c>
       <c r="K24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M24" t="s">
         <v>143</v>
@@ -3467,20 +3904,23 @@
       <c r="N24" t="s">
         <v>144</v>
       </c>
-      <c r="S24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="25" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>145</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E25" t="s">
         <v>146</v>
@@ -3501,10 +3941,10 @@
         <v>151</v>
       </c>
       <c r="K25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M25" t="s">
         <v>152</v>
@@ -3512,20 +3952,23 @@
       <c r="N25" t="s">
         <v>153</v>
       </c>
-      <c r="S25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="26" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>154</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E26" t="s">
         <v>146</v>
@@ -3546,10 +3989,10 @@
         <v>157</v>
       </c>
       <c r="K26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M26" t="s">
         <v>158</v>
@@ -3557,20 +4000,23 @@
       <c r="N26" t="s">
         <v>159</v>
       </c>
-      <c r="S26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="27" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>160</v>
       </c>
       <c r="B27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E27" t="s">
         <v>146</v>
@@ -3591,10 +4037,10 @@
         <v>162</v>
       </c>
       <c r="K27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M27" t="s">
         <v>163</v>
@@ -3602,20 +4048,23 @@
       <c r="N27" t="s">
         <v>98</v>
       </c>
-      <c r="S27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="28" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>164</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E28" t="s">
         <v>146</v>
@@ -3636,10 +4085,10 @@
         <v>166</v>
       </c>
       <c r="K28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M28" t="s">
         <v>167</v>
@@ -3647,20 +4096,23 @@
       <c r="N28" t="s">
         <v>98</v>
       </c>
-      <c r="S28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="29" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>168</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E29" t="s">
         <v>146</v>
@@ -3681,10 +4133,10 @@
         <v>170</v>
       </c>
       <c r="K29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M29" t="s">
         <v>171</v>
@@ -3692,20 +4144,23 @@
       <c r="N29" t="s">
         <v>98</v>
       </c>
-      <c r="S29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="30" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>172</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E30" t="s">
         <v>146</v>
@@ -3726,10 +4181,10 @@
         <v>174</v>
       </c>
       <c r="K30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M30" t="s">
         <v>175</v>
@@ -3737,20 +4192,23 @@
       <c r="N30" t="s">
         <v>98</v>
       </c>
-      <c r="S30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="31" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>176</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E31" t="s">
         <v>146</v>
@@ -3771,10 +4229,10 @@
         <v>178</v>
       </c>
       <c r="K31" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M31" t="s">
         <v>179</v>
@@ -3782,20 +4240,23 @@
       <c r="N31" t="s">
         <v>98</v>
       </c>
-      <c r="S31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="32" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>180</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E32" t="s">
         <v>146</v>
@@ -3816,10 +4277,10 @@
         <v>182</v>
       </c>
       <c r="K32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M32" t="s">
         <v>119</v>
@@ -3827,20 +4288,23 @@
       <c r="N32" t="s">
         <v>120</v>
       </c>
-      <c r="S32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="33" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>183</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E33" t="s">
         <v>146</v>
@@ -3861,10 +4325,10 @@
         <v>53</v>
       </c>
       <c r="K33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M33" t="s">
         <v>185</v>
@@ -3872,20 +4336,23 @@
       <c r="N33" t="s">
         <v>186</v>
       </c>
-      <c r="S33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="34" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>187</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E34" t="s">
         <v>146</v>
@@ -3906,10 +4373,10 @@
         <v>189</v>
       </c>
       <c r="K34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M34" t="s">
         <v>190</v>
@@ -3917,20 +4384,23 @@
       <c r="N34" t="s">
         <v>191</v>
       </c>
-      <c r="S34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="35" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>192</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E35" t="s">
         <v>146</v>
@@ -3951,10 +4421,10 @@
         <v>194</v>
       </c>
       <c r="K35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M35" t="s">
         <v>133</v>
@@ -3962,20 +4432,23 @@
       <c r="N35" t="s">
         <v>195</v>
       </c>
-      <c r="S35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="36" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>196</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E36" t="s">
         <v>146</v>
@@ -3996,10 +4469,10 @@
         <v>198</v>
       </c>
       <c r="K36" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M36" t="s">
         <v>138</v>
@@ -4007,20 +4480,23 @@
       <c r="N36" t="s">
         <v>199</v>
       </c>
-      <c r="S36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="37" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>200</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E37" t="s">
         <v>146</v>
@@ -4041,10 +4517,10 @@
         <v>202</v>
       </c>
       <c r="K37" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M37" t="s">
         <v>143</v>
@@ -4052,20 +4528,23 @@
       <c r="N37" t="s">
         <v>203</v>
       </c>
-      <c r="S37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="38" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>204</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E38" t="s">
         <v>205</v>
@@ -4083,13 +4562,13 @@
         <v>209</v>
       </c>
       <c r="J38" t="s">
+        <v>32</v>
+      </c>
+      <c r="K38" t="s">
         <v>33</v>
       </c>
-      <c r="K38" t="s">
-        <v>34</v>
-      </c>
       <c r="L38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M38" t="s">
         <v>210</v>
@@ -4097,20 +4576,23 @@
       <c r="N38" t="s">
         <v>186</v>
       </c>
-      <c r="S38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="39" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>211</v>
       </c>
       <c r="B39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E39" t="s">
         <v>205</v>
@@ -4131,10 +4613,10 @@
         <v>213</v>
       </c>
       <c r="K39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M39" t="s">
         <v>214</v>
@@ -4142,20 +4624,23 @@
       <c r="N39" t="s">
         <v>215</v>
       </c>
-      <c r="S39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="40" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>216</v>
       </c>
       <c r="B40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E40" t="s">
         <v>205</v>
@@ -4176,10 +4661,10 @@
         <v>218</v>
       </c>
       <c r="K40" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M40" t="s">
         <v>218</v>
@@ -4187,20 +4672,23 @@
       <c r="N40" t="s">
         <v>186</v>
       </c>
-      <c r="S40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="41" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>219</v>
       </c>
       <c r="B41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E41" t="s">
         <v>205</v>
@@ -4221,10 +4709,10 @@
         <v>213</v>
       </c>
       <c r="K41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M41" t="s">
         <v>214</v>
@@ -4232,20 +4720,23 @@
       <c r="N41" t="s">
         <v>221</v>
       </c>
-      <c r="S41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="42" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>222</v>
       </c>
       <c r="B42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E42" t="s">
         <v>205</v>
@@ -4266,10 +4757,10 @@
         <v>224</v>
       </c>
       <c r="K42" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L42" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M42" t="s">
         <v>225</v>
@@ -4277,20 +4768,23 @@
       <c r="N42" t="s">
         <v>226</v>
       </c>
-      <c r="S42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="43" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>227</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E43" t="s">
         <v>205</v>
@@ -4311,10 +4805,10 @@
         <v>229</v>
       </c>
       <c r="K43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M43" t="s">
         <v>230</v>
@@ -4322,20 +4816,23 @@
       <c r="N43" t="s">
         <v>231</v>
       </c>
-      <c r="S43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="44" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>232</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E44" t="s">
         <v>233</v>
@@ -4356,10 +4853,10 @@
         <v>238</v>
       </c>
       <c r="K44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L44" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M44" t="s">
         <v>63</v>
@@ -4367,20 +4864,23 @@
       <c r="N44" t="s">
         <v>239</v>
       </c>
-      <c r="S44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="45" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>240</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E45" t="s">
         <v>233</v>
@@ -4401,10 +4901,10 @@
         <v>242</v>
       </c>
       <c r="K45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M45" t="s">
         <v>243</v>
@@ -4412,20 +4912,23 @@
       <c r="N45" t="s">
         <v>244</v>
       </c>
-      <c r="S45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="46" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>245</v>
       </c>
       <c r="B46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E46" t="s">
         <v>246</v>
@@ -4446,10 +4949,10 @@
         <v>251</v>
       </c>
       <c r="K46" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M46" t="s">
         <v>252</v>
@@ -4457,20 +4960,23 @@
       <c r="N46" t="s">
         <v>226</v>
       </c>
-      <c r="S46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="47" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>253</v>
       </c>
       <c r="B47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C47" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E47" t="s">
         <v>246</v>
@@ -4491,10 +4997,10 @@
         <v>255</v>
       </c>
       <c r="K47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M47" t="s">
         <v>256</v>
@@ -4502,20 +5008,23 @@
       <c r="N47" t="s">
         <v>226</v>
       </c>
-      <c r="S47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="48" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>257</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E48" t="s">
         <v>246</v>
@@ -4536,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="K48" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M48" t="s">
         <v>260</v>
@@ -4547,20 +5056,23 @@
       <c r="N48" t="s">
         <v>261</v>
       </c>
-      <c r="S48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="49" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>262</v>
       </c>
       <c r="B49" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E49" t="s">
         <v>263</v>
@@ -4581,10 +5093,10 @@
         <v>268</v>
       </c>
       <c r="K49" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M49" t="s">
         <v>269</v>
@@ -4592,727 +5104,1733 @@
       <c r="N49" t="s">
         <v>120</v>
       </c>
-      <c r="S49" s="2"/>
+      <c r="P49" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>271</v>
+      </c>
+      <c r="R49" s="2">
+        <v>46196</v>
+      </c>
+      <c r="S49" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="50" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>272</v>
+      </c>
+      <c r="B50" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" t="s">
+        <v>273</v>
+      </c>
+      <c r="F50" t="s">
+        <v>274</v>
+      </c>
+      <c r="G50" t="s">
+        <v>275</v>
+      </c>
+      <c r="H50" t="s">
+        <v>276</v>
+      </c>
+      <c r="I50" t="s">
+        <v>277</v>
+      </c>
+      <c r="J50" t="s">
+        <v>278</v>
+      </c>
+      <c r="K50" t="s">
+        <v>279</v>
+      </c>
+      <c r="L50" t="s">
+        <v>34</v>
+      </c>
+      <c r="M50" t="s">
+        <v>280</v>
+      </c>
+      <c r="N50" t="s">
+        <v>281</v>
+      </c>
+      <c r="P50" t="s">
         <v>270</v>
       </c>
-      <c r="B50" t="s">
-        <v>25</v>
-      </c>
-      <c r="C50" t="s">
-        <v>26</v>
-      </c>
-      <c r="D50" t="s">
-        <v>27</v>
-      </c>
-      <c r="E50" t="s">
-        <v>271</v>
-      </c>
-      <c r="F50" t="s">
-        <v>272</v>
-      </c>
-      <c r="G50" t="s">
-        <v>273</v>
-      </c>
-      <c r="H50" t="s">
-        <v>274</v>
-      </c>
-      <c r="I50" t="s">
-        <v>275</v>
-      </c>
-      <c r="J50" t="s">
-        <v>276</v>
-      </c>
-      <c r="K50" t="s">
-        <v>277</v>
-      </c>
-      <c r="L50" t="s">
-        <v>35</v>
-      </c>
-      <c r="M50" t="s">
-        <v>278</v>
-      </c>
-      <c r="N50" t="s">
-        <v>279</v>
-      </c>
-      <c r="S50" s="2"/>
+      <c r="Q50" t="s">
+        <v>282</v>
+      </c>
+      <c r="R50" s="2">
+        <v>46196</v>
+      </c>
+      <c r="S50" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="51" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E51" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F51" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G51" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="H51" t="s">
         <v>266</v>
       </c>
       <c r="I51" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="J51" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K51" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M51" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N51" t="s">
-        <v>287</v>
-      </c>
-      <c r="S51" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="R51" s="2"/>
+      <c r="S51" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="52" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C52" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D52" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E52" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F52" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G52" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H52" t="s">
         <v>266</v>
       </c>
       <c r="I52" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="J52" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K52" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M52" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="N52" t="s">
-        <v>295</v>
-      </c>
-      <c r="S52" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="R52" s="2"/>
+      <c r="S52" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="53" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C53" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E53" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F53" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="G53" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="H53" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="I53" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="J53" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K53" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L53" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M53" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="N53" t="s">
-        <v>304</v>
-      </c>
-      <c r="S53" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="R53" s="2"/>
+      <c r="S53" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="54" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E54" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="F54" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="G54" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H54" t="s">
         <v>266</v>
       </c>
       <c r="I54" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="J54" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K54" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L54" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M54" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N54" t="s">
-        <v>312</v>
-      </c>
-      <c r="S54" s="2"/>
+        <v>315</v>
+      </c>
+      <c r="R54" s="2"/>
+      <c r="S54" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="55" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C55" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D55" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E55" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F55" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G55" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H55" t="s">
         <v>266</v>
       </c>
       <c r="I55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="K55" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M55" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N55" t="s">
-        <v>320</v>
-      </c>
-      <c r="S55" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="R55" s="2"/>
+      <c r="S55" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="56" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C56" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D56" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E56" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F56" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G56" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="H56" t="s">
         <v>266</v>
       </c>
       <c r="I56" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="J56" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K56" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M56" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="N56" t="s">
-        <v>320</v>
-      </c>
-      <c r="S56" s="2"/>
+        <v>323</v>
+      </c>
+      <c r="R56" s="2"/>
+      <c r="S56" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="57" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B57" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C57" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D57" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E57" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F57" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="G57" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="H57" t="s">
         <v>266</v>
       </c>
       <c r="I57" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J57" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K57" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M57" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N57" t="s">
-        <v>335</v>
-      </c>
-      <c r="S57" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="R57" s="2"/>
+      <c r="S57" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="58" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C58" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D58" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E58" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F58" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G58" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H58" t="s">
         <v>266</v>
       </c>
       <c r="I58" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J58" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="K58" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M58" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="N58" t="s">
-        <v>343</v>
-      </c>
-      <c r="S58" s="2"/>
+        <v>346</v>
+      </c>
+      <c r="R58" s="2"/>
+      <c r="S58" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="59" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D59" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E59" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="F59" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="G59" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="H59" t="s">
         <v>266</v>
       </c>
       <c r="I59" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="J59" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="K59" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M59" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="N59" t="s">
-        <v>351</v>
-      </c>
-      <c r="S59" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="R59" s="2"/>
+      <c r="S59" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="60" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D60" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E60" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F60" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G60" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="H60" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="I60" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="J60" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="K60" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M60" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="N60" t="s">
-        <v>304</v>
-      </c>
-      <c r="S60" s="2"/>
+        <v>363</v>
+      </c>
+      <c r="R60" s="2"/>
+      <c r="S60" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="61" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C61" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D61" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E61" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F61" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="G61" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="H61" t="s">
         <v>266</v>
       </c>
       <c r="I61" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="J61" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K61" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M61" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="N61" t="s">
-        <v>367</v>
-      </c>
-      <c r="S61" s="2"/>
+        <v>371</v>
+      </c>
+      <c r="R61" s="2"/>
+      <c r="S61" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="62" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B62" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D62" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E62" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F62" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G62" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H62" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="I62" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="J62" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K62" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M62" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="N62" t="s">
-        <v>376</v>
-      </c>
-      <c r="S62" s="2"/>
+        <v>380</v>
+      </c>
+      <c r="R62" s="2"/>
+      <c r="S62" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="63" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B63" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C63" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E63" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F63" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="G63" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="H63" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="I63" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="J63" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="K63" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L63" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M63" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="N63" t="s">
-        <v>279</v>
-      </c>
-      <c r="S63" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="R63" s="2"/>
+      <c r="S63" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="64" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B64" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E64" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="F64" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G64" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="H64" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="I64" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="J64" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="K64" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M64" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="N64" t="s">
-        <v>279</v>
-      </c>
-      <c r="S64" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="R64" s="2"/>
+      <c r="S64" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="65" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="B65" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E65" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F65" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="G65" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="H65" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="I65" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="J65" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="K65" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L65" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M65" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="N65" t="s">
-        <v>400</v>
-      </c>
-      <c r="S65" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="R65" s="2"/>
+      <c r="S65" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="66" ht="63.75" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>405</v>
+      </c>
+      <c r="D66" t="s">
+        <v>26</v>
+      </c>
+      <c r="E66" t="s">
+        <v>406</v>
+      </c>
+      <c r="F66" t="s">
+        <v>407</v>
+      </c>
+      <c r="G66" t="s">
+        <v>408</v>
+      </c>
+      <c r="H66" t="s">
+        <v>266</v>
+      </c>
+      <c r="I66" t="s">
+        <v>312</v>
+      </c>
+      <c r="J66" t="s">
+        <v>313</v>
+      </c>
+      <c r="K66" t="s">
+        <v>279</v>
+      </c>
+      <c r="L66" t="s">
+        <v>34</v>
+      </c>
+      <c r="M66" t="s">
+        <v>409</v>
+      </c>
+      <c r="N66" t="s">
+        <v>410</v>
+      </c>
+      <c r="R66" s="2"/>
+      <c r="S66" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>411</v>
+      </c>
+      <c r="B67" t="s">
+        <v>24</v>
+      </c>
+      <c r="C67" t="s">
+        <v>25</v>
+      </c>
+      <c r="D67" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67" t="s">
+        <v>412</v>
+      </c>
+      <c r="F67" t="s">
+        <v>413</v>
+      </c>
+      <c r="G67" t="s">
+        <v>414</v>
+      </c>
+      <c r="H67" t="s">
+        <v>415</v>
+      </c>
+      <c r="I67" t="s">
+        <v>254</v>
+      </c>
+      <c r="J67" t="s">
+        <v>416</v>
+      </c>
+      <c r="K67" t="s">
+        <v>33</v>
+      </c>
+      <c r="L67" t="s">
+        <v>34</v>
+      </c>
+      <c r="M67" t="s">
+        <v>417</v>
+      </c>
+      <c r="N67" t="s">
+        <v>226</v>
+      </c>
+      <c r="O67" t="s">
+        <v>418</v>
+      </c>
+      <c r="P67" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>418</v>
+      </c>
+      <c r="R67" t="s">
+        <v>418</v>
+      </c>
+      <c r="S67" t="s">
+        <v>418</v>
+      </c>
+      <c r="T67" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>419</v>
+      </c>
+      <c r="B68" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" t="s">
+        <v>25</v>
+      </c>
+      <c r="D68" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" t="s">
+        <v>412</v>
+      </c>
+      <c r="F68" t="s">
+        <v>413</v>
+      </c>
+      <c r="G68" t="s">
+        <v>414</v>
+      </c>
+      <c r="H68" t="s">
+        <v>420</v>
+      </c>
+      <c r="I68" t="s">
+        <v>421</v>
+      </c>
+      <c r="J68" t="s">
+        <v>422</v>
+      </c>
+      <c r="K68" t="s">
+        <v>33</v>
+      </c>
+      <c r="L68" t="s">
+        <v>34</v>
+      </c>
+      <c r="M68" t="s">
+        <v>423</v>
+      </c>
+      <c r="N68" t="s">
+        <v>424</v>
+      </c>
+      <c r="O68" t="s">
+        <v>418</v>
+      </c>
+      <c r="P68" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>418</v>
+      </c>
+      <c r="R68" t="s">
+        <v>418</v>
+      </c>
+      <c r="S68" t="s">
+        <v>418</v>
+      </c>
+      <c r="T68" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>425</v>
+      </c>
+      <c r="B69" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" t="s">
+        <v>25</v>
+      </c>
+      <c r="D69" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" t="s">
+        <v>412</v>
+      </c>
+      <c r="F69" t="s">
+        <v>413</v>
+      </c>
+      <c r="G69" t="s">
+        <v>414</v>
+      </c>
+      <c r="H69" t="s">
+        <v>426</v>
+      </c>
+      <c r="I69" t="s">
+        <v>258</v>
+      </c>
+      <c r="J69" t="s">
+        <v>427</v>
+      </c>
+      <c r="K69" t="s">
+        <v>33</v>
+      </c>
+      <c r="L69" t="s">
+        <v>34</v>
+      </c>
+      <c r="M69" t="s">
+        <v>428</v>
+      </c>
+      <c r="N69" t="s">
+        <v>429</v>
+      </c>
+      <c r="O69" t="s">
+        <v>418</v>
+      </c>
+      <c r="P69" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>418</v>
+      </c>
+      <c r="R69" t="s">
+        <v>418</v>
+      </c>
+      <c r="S69" t="s">
+        <v>418</v>
+      </c>
+      <c r="T69" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>430</v>
+      </c>
+      <c r="B70" t="s">
+        <v>24</v>
+      </c>
+      <c r="C70" t="s">
+        <v>25</v>
+      </c>
+      <c r="D70" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" t="s">
+        <v>412</v>
+      </c>
+      <c r="F70" t="s">
+        <v>413</v>
+      </c>
+      <c r="G70" t="s">
+        <v>414</v>
+      </c>
+      <c r="H70" t="s">
+        <v>431</v>
+      </c>
+      <c r="I70" t="s">
+        <v>432</v>
+      </c>
+      <c r="J70" t="s">
+        <v>433</v>
+      </c>
+      <c r="K70" t="s">
+        <v>33</v>
+      </c>
+      <c r="L70" t="s">
+        <v>34</v>
+      </c>
+      <c r="M70" t="s">
+        <v>434</v>
+      </c>
+      <c r="N70" t="s">
+        <v>435</v>
+      </c>
+      <c r="O70" t="s">
+        <v>418</v>
+      </c>
+      <c r="P70" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>418</v>
+      </c>
+      <c r="R70" t="s">
+        <v>418</v>
+      </c>
+      <c r="S70" t="s">
+        <v>418</v>
+      </c>
+      <c r="T70" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>436</v>
+      </c>
+      <c r="B71" t="s">
+        <v>24</v>
+      </c>
+      <c r="C71" t="s">
+        <v>25</v>
+      </c>
+      <c r="D71" t="s">
+        <v>26</v>
+      </c>
+      <c r="E71" t="s">
+        <v>412</v>
+      </c>
+      <c r="F71" t="s">
+        <v>413</v>
+      </c>
+      <c r="G71" t="s">
+        <v>414</v>
+      </c>
+      <c r="H71" t="s">
+        <v>437</v>
+      </c>
+      <c r="I71" t="s">
+        <v>438</v>
+      </c>
+      <c r="J71" t="s">
+        <v>439</v>
+      </c>
+      <c r="K71" t="s">
+        <v>33</v>
+      </c>
+      <c r="L71" t="s">
+        <v>34</v>
+      </c>
+      <c r="M71" t="s">
+        <v>440</v>
+      </c>
+      <c r="N71" t="s">
+        <v>441</v>
+      </c>
+      <c r="O71" t="s">
+        <v>418</v>
+      </c>
+      <c r="P71" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>418</v>
+      </c>
+      <c r="R71" t="s">
+        <v>418</v>
+      </c>
+      <c r="S71" t="s">
+        <v>418</v>
+      </c>
+      <c r="T71" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>442</v>
+      </c>
+      <c r="B72" t="s">
+        <v>24</v>
+      </c>
+      <c r="C72" t="s">
+        <v>25</v>
+      </c>
+      <c r="D72" t="s">
+        <v>26</v>
+      </c>
+      <c r="E72" t="s">
+        <v>443</v>
+      </c>
+      <c r="F72" t="s">
+        <v>444</v>
+      </c>
+      <c r="G72" t="s">
+        <v>445</v>
+      </c>
+      <c r="H72" t="s">
+        <v>446</v>
+      </c>
+      <c r="I72" t="s">
+        <v>447</v>
+      </c>
+      <c r="J72" t="s">
+        <v>448</v>
+      </c>
+      <c r="K72" t="s">
+        <v>279</v>
+      </c>
+      <c r="L72" t="s">
+        <v>34</v>
+      </c>
+      <c r="M72" t="s">
+        <v>449</v>
+      </c>
+      <c r="N72" t="s">
+        <v>450</v>
+      </c>
+      <c r="O72" t="s">
+        <v>418</v>
+      </c>
+      <c r="P72" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>418</v>
+      </c>
+      <c r="R72" t="s">
+        <v>418</v>
+      </c>
+      <c r="S72" t="s">
+        <v>418</v>
+      </c>
+      <c r="T72" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>451</v>
+      </c>
+      <c r="B73" t="s">
+        <v>24</v>
+      </c>
+      <c r="C73" t="s">
+        <v>25</v>
+      </c>
+      <c r="D73" t="s">
+        <v>26</v>
+      </c>
+      <c r="E73" t="s">
+        <v>452</v>
+      </c>
+      <c r="F73" t="s">
+        <v>453</v>
+      </c>
+      <c r="G73" t="s">
+        <v>454</v>
+      </c>
+      <c r="H73" t="s">
+        <v>455</v>
+      </c>
+      <c r="I73" t="s">
+        <v>456</v>
+      </c>
+      <c r="J73" t="s">
+        <v>457</v>
+      </c>
+      <c r="K73" t="s">
+        <v>279</v>
+      </c>
+      <c r="L73" t="s">
+        <v>34</v>
+      </c>
+      <c r="M73" t="s">
+        <v>458</v>
+      </c>
+      <c r="N73" t="s">
+        <v>459</v>
+      </c>
+      <c r="O73" t="s">
+        <v>418</v>
+      </c>
+      <c r="P73" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>418</v>
+      </c>
+      <c r="R73" t="s">
+        <v>418</v>
+      </c>
+      <c r="S73" t="s">
+        <v>418</v>
+      </c>
+      <c r="T73" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>460</v>
+      </c>
+      <c r="B74" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" t="s">
+        <v>25</v>
+      </c>
+      <c r="D74" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" t="s">
+        <v>461</v>
+      </c>
+      <c r="F74" t="s">
+        <v>462</v>
+      </c>
+      <c r="G74" t="s">
+        <v>463</v>
+      </c>
+      <c r="H74" t="s">
+        <v>464</v>
+      </c>
+      <c r="I74" t="s">
+        <v>465</v>
+      </c>
+      <c r="J74" t="s">
+        <v>466</v>
+      </c>
+      <c r="K74" t="s">
+        <v>33</v>
+      </c>
+      <c r="L74" t="s">
+        <v>34</v>
+      </c>
+      <c r="M74" t="s">
+        <v>417</v>
+      </c>
+      <c r="N74" t="s">
+        <v>467</v>
+      </c>
+      <c r="O74" t="s">
+        <v>418</v>
+      </c>
+      <c r="P74" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>418</v>
+      </c>
+      <c r="R74" t="s">
+        <v>418</v>
+      </c>
+      <c r="S74" t="s">
+        <v>418</v>
+      </c>
+      <c r="T74" t="s">
+        <v>418</v>
+      </c>
+      <c r="U74" t="s">
+        <v>418</v>
+      </c>
+      <c r="V74" t="s">
+        <v>418</v>
+      </c>
+      <c r="W74" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>468</v>
+      </c>
+      <c r="B75" t="s">
+        <v>24</v>
+      </c>
+      <c r="C75" t="s">
+        <v>25</v>
+      </c>
+      <c r="D75" t="s">
+        <v>26</v>
+      </c>
+      <c r="E75" t="s">
+        <v>461</v>
+      </c>
+      <c r="F75" t="s">
+        <v>462</v>
+      </c>
+      <c r="G75" t="s">
+        <v>463</v>
+      </c>
+      <c r="H75" t="s">
+        <v>464</v>
+      </c>
+      <c r="I75" t="s">
+        <v>469</v>
+      </c>
+      <c r="J75" t="s">
+        <v>470</v>
+      </c>
+      <c r="K75" t="s">
+        <v>33</v>
+      </c>
+      <c r="L75" t="s">
+        <v>34</v>
+      </c>
+      <c r="M75" t="s">
+        <v>471</v>
+      </c>
+      <c r="N75" t="s">
+        <v>472</v>
+      </c>
+      <c r="O75" t="s">
+        <v>418</v>
+      </c>
+      <c r="P75" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>418</v>
+      </c>
+      <c r="R75" t="s">
+        <v>418</v>
+      </c>
+      <c r="S75" t="s">
+        <v>418</v>
+      </c>
+      <c r="T75" t="s">
+        <v>418</v>
+      </c>
+      <c r="U75" t="s">
+        <v>418</v>
+      </c>
+      <c r="V75" t="s">
+        <v>418</v>
+      </c>
+      <c r="W75" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>473</v>
+      </c>
+      <c r="B76" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" t="s">
+        <v>25</v>
+      </c>
+      <c r="D76" t="s">
+        <v>26</v>
+      </c>
+      <c r="E76" t="s">
+        <v>461</v>
+      </c>
+      <c r="F76" t="s">
+        <v>462</v>
+      </c>
+      <c r="G76" t="s">
+        <v>463</v>
+      </c>
+      <c r="H76" t="s">
+        <v>464</v>
+      </c>
+      <c r="I76" t="s">
+        <v>474</v>
+      </c>
+      <c r="J76" t="s">
+        <v>475</v>
+      </c>
+      <c r="K76" t="s">
+        <v>33</v>
+      </c>
+      <c r="L76" t="s">
+        <v>34</v>
+      </c>
+      <c r="M76" t="s">
+        <v>476</v>
+      </c>
+      <c r="N76" t="s">
+        <v>477</v>
+      </c>
+      <c r="O76" t="s">
+        <v>418</v>
+      </c>
+      <c r="P76" t="s">
+        <v>418</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>418</v>
+      </c>
+      <c r="R76" t="s">
+        <v>418</v>
+      </c>
+      <c r="S76" t="s">
+        <v>418</v>
+      </c>
+      <c r="T76" t="s">
+        <v>418</v>
+      </c>
+      <c r="U76" t="s">
+        <v>418</v>
+      </c>
+      <c r="V76" t="s">
+        <v>418</v>
+      </c>
+      <c r="W76" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B77" t="s">
+        <v>24</v>
+      </c>
+      <c r="C77" t="s">
+        <v>25</v>
+      </c>
+      <c r="D77" t="s">
+        <v>26</v>
+      </c>
+      <c r="E77" t="s">
+        <v>478</v>
+      </c>
+      <c r="F77" t="s">
+        <v>479</v>
+      </c>
+      <c r="G77" t="s">
+        <v>480</v>
+      </c>
+      <c r="H77" t="s">
+        <v>481</v>
+      </c>
+      <c r="I77" t="s">
+        <v>482</v>
+      </c>
+      <c r="J77" t="s">
+        <v>483</v>
+      </c>
+      <c r="K77" t="s">
+        <v>33</v>
+      </c>
+      <c r="L77" t="s">
+        <v>34</v>
+      </c>
+      <c r="M77" t="s">
+        <v>484</v>
+      </c>
+      <c r="N77" t="s">
+        <v>485</v>
+      </c>
+      <c r="P77" t="s">
+        <v>270</v>
+      </c>
+      <c r="R77" s="3">
+        <v>46200</v>
+      </c>
+      <c r="S77" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B78" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" t="s">
+        <v>25</v>
+      </c>
+      <c r="D78" t="s">
+        <v>26</v>
+      </c>
+      <c r="E78" t="s">
+        <v>309</v>
+      </c>
+      <c r="F78" t="s">
+        <v>486</v>
+      </c>
+      <c r="G78" t="s">
+        <v>487</v>
+      </c>
+      <c r="H78" t="s">
+        <v>488</v>
+      </c>
+      <c r="I78" t="s">
+        <v>489</v>
+      </c>
+      <c r="J78" t="s">
+        <v>490</v>
+      </c>
+      <c r="K78" t="s">
+        <v>279</v>
+      </c>
+      <c r="L78" t="s">
+        <v>34</v>
+      </c>
+      <c r="M78" t="s">
+        <v>491</v>
+      </c>
+      <c r="N78" t="s">
+        <v>492</v>
+      </c>
+      <c r="P78" t="s">
+        <v>270</v>
+      </c>
+      <c r="R78" s="3">
+        <v>46200</v>
+      </c>
+      <c r="S78" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B79" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79" t="s">
+        <v>25</v>
+      </c>
+      <c r="D79" t="s">
+        <v>26</v>
+      </c>
+      <c r="E79" t="s">
+        <v>309</v>
+      </c>
+      <c r="F79" t="s">
+        <v>486</v>
+      </c>
+      <c r="G79" t="s">
+        <v>487</v>
+      </c>
+      <c r="H79" t="s">
+        <v>488</v>
+      </c>
+      <c r="I79" t="s">
+        <v>493</v>
+      </c>
+      <c r="J79" t="s">
+        <v>494</v>
+      </c>
+      <c r="K79" t="s">
+        <v>279</v>
+      </c>
+      <c r="L79" t="s">
+        <v>34</v>
+      </c>
+      <c r="M79" t="s">
+        <v>495</v>
+      </c>
+      <c r="N79" t="s">
+        <v>492</v>
+      </c>
+      <c r="P79" t="s">
+        <v>270</v>
+      </c>
+      <c r="R79" s="3">
+        <v>46200</v>
+      </c>
+      <c r="S79" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B80" t="s">
+        <v>24</v>
+      </c>
+      <c r="C80" t="s">
+        <v>25</v>
+      </c>
+      <c r="D80" t="s">
+        <v>26</v>
+      </c>
+      <c r="E80" t="s">
+        <v>309</v>
+      </c>
+      <c r="F80" t="s">
+        <v>486</v>
+      </c>
+      <c r="G80" t="s">
+        <v>487</v>
+      </c>
+      <c r="H80" t="s">
+        <v>488</v>
+      </c>
+      <c r="I80" t="s">
+        <v>496</v>
+      </c>
+      <c r="J80" t="s">
+        <v>497</v>
+      </c>
+      <c r="K80" t="s">
+        <v>279</v>
+      </c>
+      <c r="L80" t="s">
+        <v>34</v>
+      </c>
+      <c r="M80" t="s">
+        <v>498</v>
+      </c>
+      <c r="N80" t="s">
+        <v>492</v>
+      </c>
+      <c r="P80" t="s">
+        <v>270</v>
+      </c>
+      <c r="R80" s="3">
+        <v>46200</v>
+      </c>
+      <c r="S80" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B81" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" t="s">
+        <v>25</v>
+      </c>
+      <c r="D81" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" t="s">
+        <v>309</v>
+      </c>
+      <c r="F81" t="s">
+        <v>486</v>
+      </c>
+      <c r="G81" t="s">
+        <v>487</v>
+      </c>
+      <c r="H81" t="s">
+        <v>488</v>
+      </c>
+      <c r="I81" t="s">
+        <v>499</v>
+      </c>
+      <c r="J81" t="s">
+        <v>500</v>
+      </c>
+      <c r="K81" t="s">
+        <v>279</v>
+      </c>
+      <c r="L81" t="s">
+        <v>34</v>
+      </c>
+      <c r="M81" t="s">
+        <v>501</v>
+      </c>
+      <c r="N81" t="s">
+        <v>492</v>
+      </c>
+      <c r="P81" t="s">
+        <v>270</v>
+      </c>
+      <c r="R81" s="3">
+        <v>46200</v>
+      </c>
+      <c r="S81" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="N2:N1048576">
@@ -5321,22 +6839,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="list" sqref="E10:E64">
-      <formula1>"TS-01,TS-02,TS-03,TS-04,TS-05,TS-06,TS-07,TS-08,TS-09,TS-10,TS-11,TA-01,TA-02,TA-03,TA-04,TA-05,TA-06,TA-07,TA-08,TA-09,TA-10,TA-11,TA-12,TA-13,TA-14,TA-15,TA-16,TA-17,TA-18,TA-19,UI-01,UI-02"</formula1>
+    <dataValidation type="list" sqref="E10:E65">
+      <formula1>"TS-01,TS-02,TS-03,TS-04,TS-05,TS-06,TS-07,TS-08,TS-09,TS-10,TS-11,TA-01,TA-02,TA-03,TA-04,TA-05,TA-06,TA-07,TA-08,TA-09,TA-10,TA-11,TA-12,TA-13,TA-14,TA-15,TA-16,TA-17,TA-18,TA-19,UI-01,UI-02,UI-03,UI-04,SEC-01"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E2:E64">
-      <formula1>"TS-01,TS-02,TS-03,TS-04,TS-05,TS-06,TS-07,TS-08,TS-09,TS-10,TS-11,TA-01,TA-02,TA-03,TA-04,TA-05,TA-06,TA-07,TA-08,TA-09,TA-10,TA-11,TA-12,TA-13,TA-14,TA-15,TA-16,TA-17,TA-18,TA-19,UI-01,UI-02"</formula1>
+    <dataValidation type="list" sqref="E2:E65">
+      <formula1>"TS-01,TS-02,TS-03,TS-04,TS-05,TS-06,TS-07,TS-08,TS-09,TS-10,TS-11,TA-01,TA-02,TA-03,TA-04,TA-05,TA-06,TA-07,TA-08,TA-09,TA-10,TA-11,TA-12,TA-13,TA-14,TA-15,TA-16,TA-17,TA-18,TA-19,UI-01,UI-02,UI-03,UI-04,SEC-01"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="K10:K64">
+    <dataValidation type="list" sqref="K10:K65">
       <formula1>"POSITIVE,NEGATIVE"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="K2:K64">
+    <dataValidation type="list" sqref="K2:K65">
       <formula1>"POSITIVE,NEGATIVE"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L10:L64">
+    <dataValidation type="list" sqref="L10:L65">
       <formula1>"SYSTEMTEST,INTEGRATION"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L2:L64">
+    <dataValidation type="list" sqref="L2:L65">
       <formula1>"SYSTEMTEST,INTEGRATION"</formula1>
     </dataValidation>
   </dataValidations>
